--- a/spreadsheets/fivemillionwatchedclub.xlsx
+++ b/spreadsheets/fivemillionwatchedclub.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF82CA79-37E4-5442-9FCA-DB5A220EC40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDFF28E5-2014-1D42-A5F3-C43B3BF06AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{A0815421-F77A-534A-8D02-AC6414EF7AB6}"/>
   </bookViews>
@@ -282,7 +282,7 @@
       <name val="Aptos"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,18 +297,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3F4F6"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -316,152 +310,69 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFE5E7EB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE5E7EB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFE5E7EB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -824,1352 +735,1353 @@
   <dimension ref="A1:AN50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.5" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="10.83203125" style="1"/>
-    <col min="26" max="26" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.83203125" style="1"/>
-    <col min="40" max="40" width="11.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="8.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.5" style="16" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.1640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" style="18" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="10.83203125" style="15"/>
+    <col min="22" max="25" width="10.83203125" style="16"/>
+    <col min="26" max="26" width="13.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="28" max="33" width="10.83203125" style="16"/>
+    <col min="34" max="34" width="13.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="36" max="38" width="10.83203125" style="16"/>
+    <col min="39" max="39" width="10.83203125" style="15"/>
+    <col min="40" max="40" width="11.83203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="10.83203125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="42" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:40" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:40" s="39" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+    <row r="2" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="5">
         <v>1999</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="6">
         <v>46084</v>
       </c>
-      <c r="E2" s="36">
+      <c r="E2" s="7">
         <v>9836</v>
       </c>
-      <c r="F2" s="36">
+      <c r="F2" s="7">
         <v>9836</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="7">
         <v>1171</v>
       </c>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36">
+      <c r="H2" s="7"/>
+      <c r="I2" s="7">
         <v>416</v>
       </c>
-      <c r="J2" s="36">
+      <c r="J2" s="7">
         <v>178</v>
       </c>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28" t="s">
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="29">
+      <c r="M2" s="6">
         <v>45750</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="6">
         <v>45763</v>
       </c>
-      <c r="O2" s="29">
+      <c r="O2" s="6">
         <v>45785</v>
       </c>
-      <c r="P2" s="29">
+      <c r="P2" s="6">
         <v>45851</v>
       </c>
-      <c r="Q2" s="29">
+      <c r="Q2" s="6">
         <v>45966</v>
       </c>
-      <c r="R2" s="29">
+      <c r="R2" s="6">
         <v>46066</v>
       </c>
-      <c r="Y2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AN2" s="40"/>
-    </row>
-    <row r="3" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+      <c r="Y2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AN2" s="9"/>
+    </row>
+    <row r="3" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="37">
+      <c r="B3" s="5">
         <v>2000</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="6">
         <v>46083</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="7">
         <v>9538</v>
       </c>
-      <c r="F3" s="38">
+      <c r="F3" s="7">
         <v>9455</v>
       </c>
-      <c r="G3" s="38">
+      <c r="G3" s="7">
         <v>1391</v>
       </c>
-      <c r="H3" s="38">
+      <c r="H3" s="7">
         <v>903</v>
       </c>
-      <c r="I3" s="38">
+      <c r="I3" s="7">
         <v>528</v>
       </c>
-      <c r="J3" s="38">
+      <c r="J3" s="7">
         <v>234</v>
       </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="30" t="s">
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="31">
+      <c r="M3" s="6">
         <v>45845</v>
       </c>
-      <c r="N3" s="31">
+      <c r="N3" s="6">
         <v>45847</v>
       </c>
-      <c r="O3" s="31">
+      <c r="O3" s="6">
         <v>45858</v>
       </c>
-      <c r="P3" s="31">
+      <c r="P3" s="6">
         <v>45889</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="6">
         <v>46033</v>
       </c>
-      <c r="R3" s="31"/>
-      <c r="Y3" s="6"/>
-      <c r="AG3" s="6"/>
-      <c r="AN3" s="6"/>
-    </row>
-    <row r="4" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="R3" s="6"/>
+      <c r="Y3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AN3" s="9"/>
+    </row>
+    <row r="4" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="5">
         <v>2023</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="6">
         <v>46076</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="7">
         <v>959</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="7">
         <v>951</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="7">
         <v>926</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="7">
         <v>753</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="7">
         <v>493</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="7">
         <v>225</v>
       </c>
-      <c r="K4" s="25"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="Y4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AN4" s="6"/>
-    </row>
-    <row r="5" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="Y4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AN4" s="9"/>
+    </row>
+    <row r="5" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="5">
         <v>2021</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="6">
         <v>46074</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="7">
         <v>1633</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="7">
         <v>1621</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="7">
         <v>1297</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="7">
         <v>751</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="7">
         <v>579</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="7">
         <v>275</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="Y5" s="6"/>
-      <c r="AG5" s="6"/>
-      <c r="AN5" s="6"/>
-    </row>
-    <row r="6" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="Y5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AN5" s="9"/>
+    </row>
+    <row r="6" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="5">
         <v>1997</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="6">
         <v>46073</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="7">
         <v>10339</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="7">
         <v>10292</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="7">
         <v>1511</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="7">
         <v>895</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="7">
         <v>524</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="7">
         <v>227</v>
       </c>
-      <c r="K6" s="25"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="Y6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AN6" s="6"/>
-    </row>
-    <row r="7" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="K6" s="4"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="Y6" s="9"/>
+      <c r="AG6" s="9"/>
+      <c r="AN6" s="9"/>
+    </row>
+    <row r="7" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="5">
         <v>2019</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="6">
         <v>46054</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="7">
         <v>2478</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="7">
         <v>2476</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="7">
         <v>1560</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="7">
         <v>1020</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="7">
         <v>625</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="7">
         <v>256</v>
       </c>
-      <c r="K7" s="25"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="Y7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AN7" s="6"/>
-    </row>
-    <row r="8" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
+      <c r="K7" s="4"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="Y7" s="9"/>
+      <c r="AG7" s="9"/>
+      <c r="AN7" s="9"/>
+    </row>
+    <row r="8" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="5">
         <v>2015</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="6">
         <v>46051</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="7">
         <v>3910</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="7">
         <v>3880</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="7">
         <v>1581</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="7">
         <v>920</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="7">
         <v>576</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="7">
         <v>284</v>
       </c>
-      <c r="K8" s="25"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="Y8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AN8" s="6"/>
-    </row>
-    <row r="9" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="Y8" s="9"/>
+      <c r="AG8" s="9"/>
+      <c r="AN8" s="9"/>
+    </row>
+    <row r="9" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="5">
         <v>2009</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="6">
         <v>46049</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="7">
         <v>6104</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="7">
         <v>6089</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="7">
         <v>1578</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="7">
         <v>959</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="7">
         <v>592</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="7">
         <v>268</v>
       </c>
-      <c r="K9" s="25"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="Y9" s="6"/>
-      <c r="AG9" s="6"/>
-      <c r="AN9" s="6"/>
-    </row>
-    <row r="10" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="Y9" s="9"/>
+      <c r="AG9" s="9"/>
+      <c r="AN9" s="9"/>
+    </row>
+    <row r="10" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="5">
         <v>2014</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="6">
         <v>46032</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="7">
         <v>4378</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="7">
         <v>4111</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="7">
         <v>1413</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="7">
         <v>898</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="7">
         <v>548</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="7">
         <v>256</v>
       </c>
-      <c r="K10" s="25"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="Y10" s="6"/>
-      <c r="AG10" s="6"/>
-      <c r="AN10" s="6"/>
-    </row>
-    <row r="11" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="Y10" s="9"/>
+      <c r="AG10" s="9"/>
+      <c r="AN10" s="9"/>
+    </row>
+    <row r="11" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="5">
         <v>2018</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="6">
         <v>46032</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="7">
         <v>2820</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="7">
         <v>2818</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="7">
         <v>1620</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="7">
         <v>1054</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="7">
         <v>662</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="7">
         <v>287</v>
       </c>
-      <c r="K11" s="25"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="Y11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AN11" s="6"/>
-    </row>
-    <row r="12" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="Y11" s="9"/>
+      <c r="AG11" s="9"/>
+      <c r="AN11" s="9"/>
+    </row>
+    <row r="12" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="5">
         <v>2019</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="6">
         <v>46021</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="7">
         <v>2307</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="7">
         <v>2226</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="7">
         <v>1576</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="7">
         <v>1065</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="7">
         <v>682</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="7">
         <v>314</v>
       </c>
-      <c r="K12" s="25"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="27"/>
-      <c r="R12" s="27"/>
-      <c r="Y12" s="6"/>
-      <c r="AG12" s="6"/>
-      <c r="AN12" s="6"/>
-    </row>
-    <row r="13" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="Y12" s="9"/>
+      <c r="AG12" s="9"/>
+      <c r="AN12" s="9"/>
+    </row>
+    <row r="13" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="5">
         <v>2013</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="6">
         <v>46003</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="7">
         <v>4387</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="7">
         <v>4371</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="7">
         <v>1594</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="7">
         <v>978</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="7">
         <v>637</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="7">
         <v>294</v>
       </c>
-      <c r="K13" s="25"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="Y13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AN13" s="6"/>
-    </row>
-    <row r="14" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="13" t="s">
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="Y13" s="9"/>
+      <c r="AG13" s="9"/>
+      <c r="AN13" s="9"/>
+    </row>
+    <row r="14" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="5">
         <v>1994</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="6">
         <v>45964</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="7">
         <v>11457</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="7">
         <v>11444</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="7">
         <v>1555</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="7">
         <v>944</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="7">
         <v>590</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="7">
         <v>274</v>
       </c>
-      <c r="K14" s="25"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="Y14" s="6"/>
-      <c r="AG14" s="6"/>
-      <c r="AN14" s="6"/>
-    </row>
-    <row r="15" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="Y14" s="9"/>
+      <c r="AG14" s="9"/>
+      <c r="AN14" s="9"/>
+    </row>
+    <row r="15" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="5">
         <v>2007</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="6">
         <v>45954</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="7">
         <v>6700</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="7">
         <v>6694</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="7">
         <v>1446</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="7">
         <v>894</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="7">
         <v>576</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="7">
         <v>269</v>
       </c>
-      <c r="K15" s="25"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="27"/>
-      <c r="Y15" s="6"/>
-      <c r="AG15" s="6"/>
-      <c r="AN15" s="6"/>
-    </row>
-    <row r="16" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="Y15" s="9"/>
+      <c r="AG15" s="9"/>
+      <c r="AN15" s="9"/>
+    </row>
+    <row r="16" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="5">
         <v>2010</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="6">
         <v>45951</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="7">
         <v>5585</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="7">
         <v>5578</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="7">
         <v>1733</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="7">
         <v>1034</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="7">
         <v>645</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="7">
         <v>283</v>
       </c>
-      <c r="K16" s="25"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
-      <c r="Y16" s="6"/>
-      <c r="AG16" s="6"/>
-      <c r="AN16" s="6"/>
-    </row>
-    <row r="17" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="Y16" s="9"/>
+      <c r="AG16" s="9"/>
+      <c r="AN16" s="9"/>
+    </row>
+    <row r="17" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="5">
         <v>2017</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="6">
         <v>45939</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="7">
         <v>3182</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="7">
         <v>3150</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="7">
         <v>1569</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="7">
         <v>969</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="7">
         <v>607</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="7">
         <v>279</v>
       </c>
-      <c r="K17" s="25"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
-      <c r="Q17" s="27"/>
-      <c r="R17" s="27"/>
-      <c r="Y17" s="6"/>
-      <c r="AG17" s="6"/>
-      <c r="AN17" s="6"/>
-    </row>
-    <row r="18" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="Y17" s="9"/>
+      <c r="AG17" s="9"/>
+      <c r="AN17" s="9"/>
+    </row>
+    <row r="18" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="5">
         <v>1994</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="6">
         <v>45938</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="7">
         <v>11464</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="7">
         <v>11352</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="7">
         <v>1657</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="7">
         <v>1001</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="7">
         <v>616</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="7">
         <v>274</v>
       </c>
-      <c r="K18" s="25"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="P18" s="27"/>
-      <c r="Q18" s="27"/>
-      <c r="R18" s="27"/>
-      <c r="Y18" s="6"/>
-      <c r="AG18" s="6"/>
-      <c r="AN18" s="6"/>
-    </row>
-    <row r="19" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="Y18" s="9"/>
+      <c r="AG18" s="9"/>
+      <c r="AN18" s="9"/>
+    </row>
+    <row r="19" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="5">
         <v>2016</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="6">
         <v>45918</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="7">
         <v>3306</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="7">
         <v>3206</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="7">
         <v>1445</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="7">
         <v>810</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="7">
         <v>542</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="7">
         <v>253</v>
       </c>
-      <c r="K19" s="25"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="27"/>
-      <c r="Q19" s="27"/>
-      <c r="R19" s="27"/>
-      <c r="Y19" s="6"/>
-      <c r="AG19" s="6"/>
-      <c r="AN19" s="6"/>
-    </row>
-    <row r="20" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13" t="s">
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="Y19" s="9"/>
+      <c r="AG19" s="9"/>
+      <c r="AN19" s="9"/>
+    </row>
+    <row r="20" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="5">
         <v>2018</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="6">
         <v>45902</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="7">
         <v>2468</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="7">
         <v>2457</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="7">
         <v>1429</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="7">
         <v>886</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="7">
         <v>587</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="7">
         <v>247</v>
       </c>
-      <c r="K20" s="25"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="Y20" s="6"/>
-      <c r="AG20" s="6"/>
-      <c r="AN20" s="6"/>
-    </row>
-    <row r="21" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="Y20" s="9"/>
+      <c r="AG20" s="9"/>
+      <c r="AN20" s="9"/>
+    </row>
+    <row r="21" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="5">
         <v>2008</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="6">
         <v>45889</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="7">
         <v>6247</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="7">
         <v>6245</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="7">
         <v>1620</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="7">
         <v>970</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="7">
         <v>592</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="7">
         <v>248</v>
       </c>
-      <c r="K21" s="25"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="27"/>
-      <c r="R21" s="27"/>
-      <c r="Y21" s="6"/>
-      <c r="AG21" s="6"/>
-      <c r="AN21" s="6"/>
-    </row>
-    <row r="22" spans="1:40" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="Y21" s="9"/>
+      <c r="AG21" s="9"/>
+      <c r="AN21" s="9"/>
+    </row>
+    <row r="22" spans="1:40" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="5">
         <v>1998</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="6">
         <v>45870</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="7">
         <v>9924</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="7">
         <v>9921</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="7">
         <v>1343</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="7">
         <v>797</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="7">
         <v>496</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="7">
         <v>200</v>
       </c>
-      <c r="K22" s="25"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="Y22" s="6"/>
-      <c r="AG22" s="6"/>
-      <c r="AN22" s="6"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="Y22" s="9"/>
+      <c r="AG22" s="9"/>
+      <c r="AN22" s="9"/>
     </row>
     <row r="23" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="5">
         <v>2019</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="6">
         <v>45771</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="7">
         <v>2064</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="7">
         <v>2033</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="7">
         <v>1448</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="7">
         <v>904</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="7">
         <v>533</v>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="7">
         <v>259</v>
       </c>
-      <c r="K23" s="26"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
     </row>
     <row r="24" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="5">
         <v>2019</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="6">
         <v>45751</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="7">
         <v>2146</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="7">
         <v>2137</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="7">
         <v>1455</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="7">
         <v>898</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="7">
         <v>526</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="7">
         <v>239</v>
       </c>
-      <c r="K24" s="26"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="27"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
     </row>
     <row r="25" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="19">
+      <c r="B25" s="5">
         <v>2014</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="6">
         <v>45745</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="7">
         <v>3808</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="7">
         <v>3798</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="7">
         <v>1327</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="7">
         <v>737</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="7">
         <v>432</v>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="7">
         <v>145</v>
       </c>
-      <c r="K25" s="26"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
     </row>
     <row r="26" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="5">
         <v>1999</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="6">
         <v>45740</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="7">
         <v>9328</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="7">
         <v>9293</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="7">
         <v>1386</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="7">
         <v>811</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="7">
         <v>465</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="7">
         <v>220</v>
       </c>
-      <c r="K26" s="26"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
     </row>
     <row r="27" spans="1:40" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B27" s="5">
         <v>2023</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="6">
         <v>45714</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="7">
         <v>599</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="7">
         <v>589</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="7">
         <v>578</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="7">
         <v>496</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="7">
         <v>384</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="7">
         <v>187</v>
       </c>
-      <c r="K27" s="26"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="L28" s="3"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="7"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="21"/>
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="L29" s="3"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="7"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="21"/>
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="L30" s="3"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="7"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="21"/>
     </row>
     <row r="31" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="L31" s="3"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="7"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="21"/>
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="L32" s="3"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="7"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="21"/>
     </row>
     <row r="33" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L33" s="3"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="7"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="21"/>
     </row>
     <row r="34" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L34" s="3"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="7"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="21"/>
     </row>
     <row r="35" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L35" s="3"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="7"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="21"/>
     </row>
     <row r="36" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L36" s="3"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="7"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="21"/>
     </row>
     <row r="37" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L37" s="3"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="7"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="21"/>
     </row>
     <row r="38" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L38" s="3"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="7"/>
+      <c r="L38" s="19"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="21"/>
     </row>
     <row r="39" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L39" s="3"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="7"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="21"/>
     </row>
     <row r="40" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L40" s="3"/>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8"/>
-      <c r="O40" s="7"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="21"/>
     </row>
     <row r="41" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L41" s="3"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="7"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="21"/>
     </row>
     <row r="42" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L42" s="3"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="7"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="21"/>
     </row>
     <row r="43" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L43" s="3"/>
-      <c r="M43" s="8"/>
-      <c r="N43" s="8"/>
-      <c r="O43" s="7"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="21"/>
     </row>
     <row r="44" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L44" s="3"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="8"/>
-      <c r="O44" s="7"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="21"/>
     </row>
     <row r="45" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L45" s="3"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="7"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="21"/>
     </row>
     <row r="46" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L46" s="3"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="7"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="20"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="21"/>
     </row>
     <row r="47" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L47" s="3"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="7"/>
+      <c r="L47" s="19"/>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="21"/>
     </row>
     <row r="48" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L48" s="3"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="7"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="21"/>
     </row>
     <row r="49" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L49" s="3"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="7"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="21"/>
     </row>
     <row r="50" spans="12:15" x14ac:dyDescent="0.2">
-      <c r="L50" s="3"/>
-      <c r="M50" s="8"/>
-      <c r="N50" s="8"/>
-      <c r="O50" s="7"/>
+      <c r="L50" s="19"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
